--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.41344692154852</v>
+        <v>9.492185124751634</v>
       </c>
       <c r="D2" t="n">
-        <v>59.07350163959946</v>
+        <v>9.599444016434912</v>
       </c>
       <c r="E2" t="n">
-        <v>18.73976072842806</v>
+        <v>3.04521111836956</v>
       </c>
       <c r="F2" t="n">
-        <v>19.8143886840356</v>
+        <v>3.219838161155784</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>69.52980651027571</v>
+        <v>11.2985935579198</v>
       </c>
       <c r="D3" t="n">
-        <v>70.33385254307701</v>
+        <v>11.42925103825002</v>
       </c>
       <c r="E3" t="n">
-        <v>18.73976072842806</v>
+        <v>3.04521111836956</v>
       </c>
       <c r="F3" t="n">
-        <v>19.8143886840356</v>
+        <v>3.219838161155784</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.21688212630274</v>
+        <v>6.210243345524196</v>
       </c>
       <c r="D4" t="n">
-        <v>38.98042849285982</v>
+        <v>6.33431963008972</v>
       </c>
       <c r="E4" t="n">
-        <v>18.73976072842806</v>
+        <v>3.04521111836956</v>
       </c>
       <c r="F4" t="n">
-        <v>19.8143886840356</v>
+        <v>3.219838161155784</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.95174792162664</v>
+        <v>2.75465903726433</v>
       </c>
       <c r="D5" t="n">
-        <v>17.43538885435456</v>
+        <v>2.833250688832617</v>
       </c>
       <c r="E5" t="n">
-        <v>18.73976072842806</v>
+        <v>3.04521111836956</v>
       </c>
       <c r="F5" t="n">
-        <v>19.8143886840356</v>
+        <v>3.219838161155784</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.39236383927099</v>
+        <v>3.151259123881536</v>
       </c>
       <c r="D6" t="n">
-        <v>18.59640915966435</v>
+        <v>3.021916488445457</v>
       </c>
       <c r="E6" t="n">
-        <v>18.73976072842806</v>
+        <v>3.04521111836956</v>
       </c>
       <c r="F6" t="n">
-        <v>19.8143886840356</v>
+        <v>3.219838161155784</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.33704212993257</v>
+        <v>4.117269346114043</v>
       </c>
       <c r="D7" t="n">
-        <v>19.07287508007165</v>
+        <v>3.099342200511644</v>
       </c>
       <c r="E7" t="n">
-        <v>18.73976072842806</v>
+        <v>3.04521111836956</v>
       </c>
       <c r="F7" t="n">
-        <v>19.8143886840356</v>
+        <v>3.219838161155784</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>48.65238801918436</v>
+        <v>7.906013053117459</v>
       </c>
       <c r="D8" t="n">
-        <v>48.23662776550239</v>
+        <v>7.838452011894139</v>
       </c>
       <c r="E8" t="n">
-        <v>18.73976072842806</v>
+        <v>3.04521111836956</v>
       </c>
       <c r="F8" t="n">
-        <v>19.8143886840356</v>
+        <v>3.219838161155784</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
